--- a/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
+++ b/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
@@ -13,10 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_装备模板" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_词缀目录" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_套装效果" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_至宝配装基准" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_掉落等级带" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_实现差异" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_来源校验" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_套装术语" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_至宝配装基准" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_掉落等级带" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_实现差异" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_来源校验" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_说明'!$A$1:$B$9</definedName>
@@ -25,10 +26,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_装备模板'!$A$1:$H$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_词缀目录'!$A$1:$I$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_套装效果'!$A$1:$G$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_至宝配装基准'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_掉落等级带'!$A$1:$F$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_实现差异'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_来源校验'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'05A_套装术语'!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'06_至宝配装基准'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'07_掉落等级带'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'08_实现差异'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'09_来源校验'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -642,7 +644,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>当前运行时代码仍是旧曲线/旧宝石规则；本表是批准设计，不冒充已实装</t>
+          <t>装备基础曲线/宝石仍按差异表追踪；六套2／4／6件效果已实装，玄甲/山河采用v35语义</t>
         </is>
       </c>
     </row>
@@ -658,7 +660,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>当前旧实现</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>批准新设计</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>装备基础贡献</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>当前代码使用旧完整曲线</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>新设计生命/攻击/防御贡献约减半</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>待实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>宝石生命</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>当前代码为同阶攻防的10倍</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>新设计为5倍</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>待实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>不朽后成长</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>当前代码继续×2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>新设计约×1.25并向上取整</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>待实现</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>至宝孔位</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>当前代码按品质公式得到2孔</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>新设计至宝整套共12孔，即每件2孔</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>装备内力</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>旧ID/快照仍可读</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>有效贡献恒为0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>基础规则已冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>玄甲/山河套装</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>旧描述符缺少完整消费者</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>六档批准语义与触发顺序</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>已实装并迁移至v35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>百级最终属性</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>旧运行时投影不同</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>使用01表批准数值</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>设计冻结、运行时待迁移</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="85" customWidth="1" min="1" max="1"/>
@@ -692,17 +891,41 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>docs\superpowers\specs\2026-09-04-xuanjia-shanhe-set-design.md</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>20fd4db40aaa3fba6113c0975113c93192a85a76d3a7dcb2cf459f24499ce208</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Source\GameXXK\Private\GameXXKEquipmentCatalog.cpp</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>767776be3c0d6809e9f5eac782270ca8a984743a0cd2027da5d06f48ad5a8f46</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Source\GameXXK\Private\GameXXKEquipmentSetCatalog.cpp</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>f1137fa7394b30778a9b9a35bd6e0c798adca328896e9d2b3900743a67e77f80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6212,17 +6435,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>产生护甲</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>获得的护甲提高5%。</t>
+          <t>穿戴者产生的护甲提高10%。</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>仅描述符；玄甲现行目标与阶位待评审</t>
+          <t>已批准；消费者已实装</t>
         </is>
       </c>
     </row>
@@ -6247,17 +6470,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>回合开始</t>
+          <t>回合开始／首次格挡</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>回合开始保留护甲并使首次直接受击反击80%。</t>
+          <t>我方回合开始时保留50%护甲；每个敌方回合首次格挡后，追加80%攻击伤害。</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>仅描述符；已确认意图为保留50%护甲，阶位/取整待评审</t>
+          <t>已批准；消费者已实装</t>
         </is>
       </c>
     </row>
@@ -6277,22 +6500,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>全队</t>
+          <t>全队唯一</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>首次友方生命受伤</t>
+          <t>首次攻击气血伤害</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>每回合首次有友方受到气血伤害时，为全队提供1次护甲与护援。</t>
+          <t>全队唯一。敌方回合首次有友方因攻击损失气血后，全体获得穿戴者40%防御的护甲；穿戴者援护其他友方各1次。</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>仅描述符；无战斗消费者</t>
+          <t>已批准；消费者已实装</t>
         </is>
       </c>
     </row>
@@ -6632,17 +6855,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>首张地势牌</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>当前地形效果提高5%。</t>
+          <t>每回合首次打出地势牌后，抽1张。</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>仅描述符；待评审</t>
+          <t>已批准；消费者已实装</t>
         </is>
       </c>
     </row>
@@ -6667,17 +6890,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>首张地形联动牌</t>
+          <t>首张地势牌</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>费用降低1并强化相邻队友。</t>
+          <t>每回合首张地势牌少耗1气；结算后，其他友方各回复2内力。</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>仅描述符；相邻/增益/取整待评审</t>
+          <t>已批准；消费者已实装</t>
         </is>
       </c>
     </row>
@@ -6697,22 +6920,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>全队</t>
+          <t>全队唯一</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>被动</t>
+          <t>我方回合开始</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>当前地形成为阵眼，向全队提供12%对应增益。</t>
+          <t>全队唯一。每个我方回合开始时，由穿戴者触发1次当前地势。</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>仅描述符；无战斗消费者</t>
+          <t>已批准；消费者已实装</t>
         </is>
       </c>
     </row>
@@ -6723,6 +6946,61 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>术语</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>玩家说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>地势牌</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>会改变或触发地势的主动牌。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>全队唯一</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>同名团队套装只生效1份。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6896,7 +7174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7597,179 +7875,4 @@
   <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>当前旧实现</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>批准新设计</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>装备基础贡献</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>当前代码使用旧完整曲线</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>新设计生命/攻击/防御贡献约减半</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>待实现</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>宝石生命</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>当前代码为同阶攻防的10倍</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>新设计为5倍</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>待实现</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>不朽后成长</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>当前代码继续×2</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>新设计约×1.25并向上取整</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>待实现</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>至宝孔位</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>当前代码按品质公式得到2孔</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>新设计至宝整套共12孔，即每件2孔</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>装备内力</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>旧ID/快照仍可读</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>有效贡献恒为0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>基础规则已冻结</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>百级最终属性</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>旧运行时投影不同</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>使用01表批准数值</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>设计冻结、运行时待迁移</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
+++ b/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>装备基础曲线/宝石仍按差异表追踪；六套2／4／6件效果已实装，玄甲/山河采用v35语义</t>
+          <t>装备基础曲线/宝石仍按差异表追踪；六套2／4／6件效果已实装，玄甲/山河由v35引入且当前v36保持同一语义</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>已实装并迁移至v35</t>
+          <t>已实装；v35引入，当前v36保留</t>
         </is>
       </c>
     </row>

--- a/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
+++ b/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
@@ -15,31 +15,32 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04E_一至六件边际" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04F_递减曲线" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04G_详细属性口径" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04C_名称显示入口" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_套装效果" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_套装术语" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_实现差异" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_百级最终属性" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_宝石总表" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_宝石品质边际" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_装备模板" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_至宝配装基准" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_掉落等级带" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_挂机金币现状" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07B_分解与工具经验" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07C_经济与工具边界" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07D_宝箱与行旅钱" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_来源校验" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02B_百分比宝石数值" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02C_宝石收益与表现" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07E_挂机与天赋预算" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07F_天赋分档价格" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04H_追风递增与退休" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04C_名称显示入口" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_套装效果" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_套装术语" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_实现差异" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_百级最终属性" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_宝石总表" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_宝石品质边际" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_装备模板" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_至宝配装基准" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_掉落等级带" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_挂机金币现状" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07B_分解与工具经验" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07C_经济与工具边界" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07D_宝箱与行旅钱" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_来源校验" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02B_百分比宝石数值" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02C_宝石收益与表现" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07E_挂机与天赋预算" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07F_天赋分档价格" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_说明'!$A$1:$B$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'00_说明'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'00_说明'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'04_词缀目录'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'04_词缀目录'!$A$1:$L$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'04_词缀目录'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'04_词缀目录'!$A$1:$J$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'04A_触发与接入审查'!$A$1:$I$31</definedName>
@@ -60,55 +61,57 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'04G_详细属性口径'!$A$1:$C$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'04G_详细属性口径'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'04G_详细属性口径'!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'04C_名称显示入口'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'04C_名称显示入口'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'04C_名称显示入口'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'05_套装效果'!$A$1:$I$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'05_套装效果'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'05_套装效果'!$A$1:$I$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'05A_套装术语'!$A$1:$B$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'05A_套装术语'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'05A_套装术语'!$A$1:$B$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'08_实现差异'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'08_实现差异'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'08_实现差异'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'01_百级最终属性'!$A$1:$L$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'01_百级最终属性'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'01_百级最终属性'!$A$1:$L$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'02_宝石总表'!$A$1:$L$141</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'02_宝石总表'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'02_宝石总表'!$A$1:$L$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'02A_宝石品质边际'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'02A_宝石品质边际'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'02A_宝石品质边际'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'03_装备模板'!$A$1:$N$50</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'03_装备模板'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'03_装备模板'!$A$1:$N$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'06_至宝配装基准'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'06_至宝配装基准'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'06_至宝配装基准'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'07_掉落等级带'!$A$1:$I$28</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'07_掉落等级带'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'07_掉落等级带'!$A$1:$I$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'07A_挂机金币现状'!$A$1:$H$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'07B_分解与工具经验'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="19">'07B_分解与工具经验'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">'07B_分解与工具经验'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'07C_经济与工具边界'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="20">'07C_经济与工具边界'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="20">'07C_经济与工具边界'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'07D_宝箱与行旅钱'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'09_来源校验'!$A$1:$C$35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="22">'09_来源校验'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="22">'09_来源校验'!$A$1:$C$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'02B_百分比宝石数值'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="23">'02B_百分比宝石数值'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="23">'02B_百分比宝石数值'!$A$1:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'02C_宝石收益与表现'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="24">'02C_宝石收益与表现'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="24">'02C_宝石收益与表现'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'07E_挂机与天赋预算'!$A$1:$C$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'07F_天赋分档价格'!$A$1:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'04H_追风递增与退休'!$A$4:$D$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'04H_追风递增与退休'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'04C_名称显示入口'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'04C_名称显示入口'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'04C_名称显示入口'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'05_套装效果'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'05_套装效果'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'05_套装效果'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'05A_套装术语'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'05A_套装术语'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'05A_套装术语'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'08_实现差异'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'08_实现差异'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'08_实现差异'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'01_百级最终属性'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'01_百级最终属性'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'01_百级最终属性'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'02_宝石总表'!$A$1:$M$141</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'02_宝石总表'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'02_宝石总表'!$A$1:$L$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'02A_宝石品质边际'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'02A_宝石品质边际'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'02A_宝石品质边际'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'03_装备模板'!$A$1:$Q$50</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'03_装备模板'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'03_装备模板'!$A$1:$N$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'06_至宝配装基准'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'06_至宝配装基准'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'06_至宝配装基准'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'07_掉落等级带'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'07_掉落等级带'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'07_掉落等级带'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'07A_挂机金币现状'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'07B_分解与工具经验'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="20">'07B_分解与工具经验'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'07B_分解与工具经验'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'07C_经济与工具边界'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="21">'07C_经济与工具边界'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'07C_经济与工具边界'!$A$1:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'07D_宝箱与行旅钱'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'09_来源校验'!$A$1:$C$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="23">'09_来源校验'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'09_来源校验'!$A$1:$C$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'02B_百分比宝石数值'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="24">'02B_百分比宝石数值'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'02B_百分比宝石数值'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'02C_宝石收益与表现'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="25">'02C_宝石收益与表现'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'02C_宝石收益与表现'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'07E_挂机与天赋预算'!$A$1:$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'07F_天赋分档价格'!$A$1:$D$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -122,7 +125,7 @@
     <numFmt numFmtId="166" formatCode="0.00&quot; 个百分点&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;×&quot;0.00##"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -162,8 +165,33 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00183F3A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="0062766F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00243E38"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -250,6 +278,16 @@
         <fgColor rgb="00F1F5F4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00244C45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F5EF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -273,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -378,6 +416,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1345,6 +1401,220 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="67" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>入口</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>代码当前行为</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>名称状态</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>核对范围</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>源码定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="39" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>统一装备提示</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>使用ModifierLabel + 数值/百分比；最大内力词缀直接隐藏。</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>已直接描述效果</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>这是总表词缀名称的取值来源。</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="39" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>桌面背包装备格</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>调用统一装备提示Build/Bind。</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>已直接描述效果</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>当前默认桌面工作台入口。</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/UI/GameXXKDesktopTrainingWorkbenchWidget.cpp:6565</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="39" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>桌面商店结果卡</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>调用统一装备提示Build/Bind。</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>已直接描述效果</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>当前桌面商店购买结果入口。</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/UI/GameXXKDesktopTrainingWorkbenchWidget.cpp:4536</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>旧商店控件</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>仍有读取Affix-&gt;DisplayName的格式化代码。</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>仍保留旧短名路径</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>源码事实；本轮未验证旧控件在当前流程的可达性。</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/UI/GameXXKMetaShopWidget.cpp:132</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="29" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>旧伙伴名册控件</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>仍有读取Affix-&gt;DisplayName的格式化代码。</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>仍保留旧短名路径</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>源码事实；本轮未验证旧控件在当前流程的可达性。</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/UI/GameXXKCompanionRosterWidget.cpp:468</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>词缀目录内部字段</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>DisplayName仍保留旧别名；稳定ID用于实例和存档解析。</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>内部字段未改名</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>总表主名称不再采用旧别名；不把显示更新误写成C++字段已修改。</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E7"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00244D57"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2224,7 +2494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
@@ -2366,7 +2636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BA6650"/>
@@ -2445,17 +2715,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>30条均可生成并投影；仅护甲获得量定位到实际消费者。</t>
+          <t>当前26个分系随机项；产甲和乘风已接入并验证，其余24项待接入。</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>逐条审查29条未接入效果；不是18条套装都失效。</t>
+          <t>24项仍需触发/运行时接入；不等同固定套装失效。</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>29条未找到消费者；1条已接入</t>
+          <t>2项已验证；24项待接入</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -2715,7 +2985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B8B68"/>
@@ -3145,14 +3415,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3167,6 +3437,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3230,6 +3501,11 @@
           <t>当前状态</t>
         </is>
       </c>
+      <c r="M1" s="36" t="inlineStr">
+        <is>
+          <t>英文名称</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="39" customHeight="1">
       <c r="A2" s="21" t="n">
@@ -3242,7 +3518,7 @@
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>普通攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D2" s="21" t="n">
@@ -3280,6 +3556,11 @@
       <c r="L2" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M2" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3575,7 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>普通防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D3" s="22" t="n">
@@ -3332,6 +3613,11 @@
       <c r="L3" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M3" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3632,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>普通生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D4" s="21" t="n">
@@ -3384,6 +3670,11 @@
       <c r="L4" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M4" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3689,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>普通攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D5" s="22" t="n">
@@ -3436,6 +3727,11 @@
       <c r="L5" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M5" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3746,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>普通防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D6" s="21" t="n">
@@ -3488,6 +3784,11 @@
       <c r="L6" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M6" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3803,7 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>普通生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D7" s="22" t="n">
@@ -3540,6 +3841,11 @@
       <c r="L7" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M7" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3860,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>普通直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D8" s="21" t="n">
@@ -3592,6 +3898,11 @@
       <c r="L8" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M8" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3917,7 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>普通护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D9" s="22" t="n">
@@ -3644,6 +3955,11 @@
       <c r="L9" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M9" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3974,7 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>普通治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D10" s="21" t="n">
@@ -3696,6 +4012,11 @@
       <c r="L10" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M10" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -3710,7 +4031,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>普通反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D11" s="22" t="n">
@@ -3748,6 +4069,11 @@
       <c r="L11" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M11" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -3762,7 +4088,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>普通火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D12" s="21" t="n">
@@ -3800,6 +4126,11 @@
       <c r="L12" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M12" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -3814,7 +4145,7 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>普通持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D13" s="22" t="n">
@@ -3852,6 +4183,11 @@
       <c r="L13" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M13" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -3866,7 +4202,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>普通冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D14" s="21" t="n">
@@ -3904,6 +4240,11 @@
       <c r="L14" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M14" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -3918,7 +4259,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>普通雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D15" s="22" t="n">
@@ -3956,6 +4297,11 @@
       <c r="L15" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M15" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -3970,7 +4316,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>稀有攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D16" s="21" t="n">
@@ -4008,6 +4354,11 @@
       <c r="L16" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M16" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4373,7 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>稀有防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D17" s="22" t="n">
@@ -4060,6 +4411,11 @@
       <c r="L17" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M17" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4430,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>稀有生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D18" s="21" t="n">
@@ -4112,6 +4468,11 @@
       <c r="L18" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M18" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4487,7 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>稀有攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D19" s="22" t="n">
@@ -4164,6 +4525,11 @@
       <c r="L19" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M19" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4544,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>稀有防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D20" s="21" t="n">
@@ -4216,6 +4582,11 @@
       <c r="L20" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M20" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4601,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>稀有生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D21" s="22" t="n">
@@ -4268,6 +4639,11 @@
       <c r="L21" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M21" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4658,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>稀有直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D22" s="21" t="n">
@@ -4320,6 +4696,11 @@
       <c r="L22" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M22" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4715,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>稀有护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D23" s="22" t="n">
@@ -4372,6 +4753,11 @@
       <c r="L23" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M23" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4772,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>稀有治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D24" s="21" t="n">
@@ -4424,6 +4810,11 @@
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M24" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4829,7 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>稀有反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D25" s="22" t="n">
@@ -4476,6 +4867,11 @@
       <c r="L25" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M25" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4886,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>稀有火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D26" s="21" t="n">
@@ -4528,6 +4924,11 @@
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M26" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4943,7 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>稀有持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D27" s="22" t="n">
@@ -4580,6 +4981,11 @@
       <c r="L27" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M27" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -4594,7 +5000,7 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>稀有冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D28" s="21" t="n">
@@ -4632,6 +5038,11 @@
       <c r="L28" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M28" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -4646,7 +5057,7 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>稀有雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D29" s="22" t="n">
@@ -4684,6 +5095,11 @@
       <c r="L29" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M29" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -4698,7 +5114,7 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>珍稀攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D30" s="21" t="n">
@@ -4736,6 +5152,11 @@
       <c r="L30" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M30" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -4750,7 +5171,7 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>珍稀防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D31" s="22" t="n">
@@ -4788,6 +5209,11 @@
       <c r="L31" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M31" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -4802,7 +5228,7 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>珍稀生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D32" s="21" t="n">
@@ -4840,6 +5266,11 @@
       <c r="L32" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M32" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -4854,7 +5285,7 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>珍稀攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D33" s="22" t="n">
@@ -4892,6 +5323,11 @@
       <c r="L33" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M33" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -4906,7 +5342,7 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>珍稀防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D34" s="21" t="n">
@@ -4944,6 +5380,11 @@
       <c r="L34" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M34" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -4958,7 +5399,7 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>珍稀生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D35" s="22" t="n">
@@ -4996,6 +5437,11 @@
       <c r="L35" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M35" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5456,7 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>珍稀直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D36" s="21" t="n">
@@ -5048,6 +5494,11 @@
       <c r="L36" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M36" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5513,7 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>珍稀护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
@@ -5100,6 +5551,11 @@
       <c r="L37" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M37" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5570,7 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>珍稀治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D38" s="21" t="n">
@@ -5152,6 +5608,11 @@
       <c r="L38" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M38" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5627,7 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>珍稀反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D39" s="22" t="n">
@@ -5204,6 +5665,11 @@
       <c r="L39" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M39" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5684,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>珍稀火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D40" s="21" t="n">
@@ -5256,6 +5722,11 @@
       <c r="L40" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M40" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5741,7 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>珍稀持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D41" s="22" t="n">
@@ -5308,6 +5779,11 @@
       <c r="L41" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M41" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5798,7 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>珍稀冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D42" s="21" t="n">
@@ -5360,6 +5836,11 @@
       <c r="L42" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M42" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5855,7 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>珍稀雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D43" s="22" t="n">
@@ -5412,6 +5893,11 @@
       <c r="L43" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M43" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5912,7 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>传奇攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D44" s="21" t="n">
@@ -5464,6 +5950,11 @@
       <c r="L44" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M44" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5969,7 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>传奇防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D45" s="22" t="n">
@@ -5516,6 +6007,11 @@
       <c r="L45" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M45" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -5530,7 +6026,7 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>传奇生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D46" s="21" t="n">
@@ -5568,6 +6064,11 @@
       <c r="L46" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M46" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -5582,7 +6083,7 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>传奇攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D47" s="22" t="n">
@@ -5620,6 +6121,11 @@
       <c r="L47" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M47" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -5634,7 +6140,7 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>传奇防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D48" s="21" t="n">
@@ -5672,6 +6178,11 @@
       <c r="L48" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M48" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -5686,7 +6197,7 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>传奇生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
@@ -5724,6 +6235,11 @@
       <c r="L49" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M49" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -5738,7 +6254,7 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>传奇直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D50" s="21" t="n">
@@ -5776,6 +6292,11 @@
       <c r="L50" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M50" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -5790,7 +6311,7 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>传奇护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D51" s="22" t="n">
@@ -5828,6 +6349,11 @@
       <c r="L51" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M51" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -5842,7 +6368,7 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>传奇治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D52" s="21" t="n">
@@ -5880,6 +6406,11 @@
       <c r="L52" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M52" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -5894,7 +6425,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>传奇反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D53" s="22" t="n">
@@ -5932,6 +6463,11 @@
       <c r="L53" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M53" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -5946,7 +6482,7 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>传奇火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D54" s="21" t="n">
@@ -5984,6 +6520,11 @@
       <c r="L54" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M54" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -5998,7 +6539,7 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>传奇持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D55" s="22" t="n">
@@ -6036,6 +6577,11 @@
       <c r="L55" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M55" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6596,7 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>传奇冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D56" s="21" t="n">
@@ -6088,6 +6634,11 @@
       <c r="L56" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M56" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6653,7 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>传奇雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D57" s="22" t="n">
@@ -6140,6 +6691,11 @@
       <c r="L57" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M57" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6710,7 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>不朽攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D58" s="21" t="n">
@@ -6192,6 +6748,11 @@
       <c r="L58" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M58" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6767,7 @@
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>不朽防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D59" s="22" t="n">
@@ -6244,6 +6805,11 @@
       <c r="L59" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M59" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6824,7 @@
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>不朽生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D60" s="21" t="n">
@@ -6296,6 +6862,11 @@
       <c r="L60" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M60" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6881,7 @@
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>不朽攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D61" s="22" t="n">
@@ -6348,6 +6919,11 @@
       <c r="L61" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M61" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6938,7 @@
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>不朽防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D62" s="21" t="n">
@@ -6400,6 +6976,11 @@
       <c r="L62" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M62" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6995,7 @@
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>不朽生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D63" s="22" t="n">
@@ -6452,6 +7033,11 @@
       <c r="L63" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M63" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -6466,7 +7052,7 @@
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>不朽直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D64" s="21" t="n">
@@ -6504,6 +7090,11 @@
       <c r="L64" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M64" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -6518,7 +7109,7 @@
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>不朽护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D65" s="22" t="n">
@@ -6556,6 +7147,11 @@
       <c r="L65" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M65" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -6570,7 +7166,7 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>不朽治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D66" s="21" t="n">
@@ -6608,6 +7204,11 @@
       <c r="L66" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M66" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -6622,7 +7223,7 @@
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>不朽反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D67" s="22" t="n">
@@ -6660,6 +7261,11 @@
       <c r="L67" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M67" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -6674,7 +7280,7 @@
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>不朽火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D68" s="21" t="n">
@@ -6712,6 +7318,11 @@
       <c r="L68" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M68" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -6726,7 +7337,7 @@
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>不朽持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
@@ -6764,6 +7375,11 @@
       <c r="L69" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M69" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -6778,7 +7394,7 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>不朽冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D70" s="21" t="n">
@@ -6816,6 +7432,11 @@
       <c r="L70" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M70" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -6830,7 +7451,7 @@
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>不朽雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D71" s="22" t="n">
@@ -6868,6 +7489,11 @@
       <c r="L71" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M71" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -6882,7 +7508,7 @@
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>至宝攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D72" s="21" t="n">
@@ -6920,6 +7546,11 @@
       <c r="L72" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M72" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -6934,7 +7565,7 @@
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>至宝防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D73" s="22" t="n">
@@ -6972,6 +7603,11 @@
       <c r="L73" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M73" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -6986,7 +7622,7 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>至宝生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D74" s="21" t="n">
@@ -7024,6 +7660,11 @@
       <c r="L74" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M74" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7679,7 @@
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>至宝攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
@@ -7076,6 +7717,11 @@
       <c r="L75" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M75" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7736,7 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>至宝防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D76" s="21" t="n">
@@ -7128,6 +7774,11 @@
       <c r="L76" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M76" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7793,7 @@
       </c>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>至宝生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
@@ -7180,6 +7831,11 @@
       <c r="L77" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M77" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7850,7 @@
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>至宝直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D78" s="21" t="n">
@@ -7232,6 +7888,11 @@
       <c r="L78" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M78" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7907,7 @@
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>至宝护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D79" s="22" t="n">
@@ -7284,6 +7945,11 @@
       <c r="L79" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M79" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7964,7 @@
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>至宝治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D80" s="21" t="n">
@@ -7336,6 +8002,11 @@
       <c r="L80" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M80" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -7350,7 +8021,7 @@
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>至宝反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D81" s="22" t="n">
@@ -7388,6 +8059,11 @@
       <c r="L81" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M81" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -7402,7 +8078,7 @@
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>至宝火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D82" s="21" t="n">
@@ -7440,6 +8116,11 @@
       <c r="L82" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M82" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -7454,7 +8135,7 @@
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>至宝持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D83" s="22" t="n">
@@ -7492,6 +8173,11 @@
       <c r="L83" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M83" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -7506,7 +8192,7 @@
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>至宝冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D84" s="21" t="n">
@@ -7544,6 +8230,11 @@
       <c r="L84" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M84" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -7558,7 +8249,7 @@
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>至宝雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D85" s="22" t="n">
@@ -7596,6 +8287,11 @@
       <c r="L85" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M85" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -7610,7 +8306,7 @@
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>超凡攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D86" s="21" t="n">
@@ -7648,6 +8344,11 @@
       <c r="L86" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M86" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -7662,7 +8363,7 @@
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>超凡防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D87" s="22" t="n">
@@ -7700,6 +8401,11 @@
       <c r="L87" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M87" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -7714,7 +8420,7 @@
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>超凡生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D88" s="21" t="n">
@@ -7752,6 +8458,11 @@
       <c r="L88" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M88" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -7766,7 +8477,7 @@
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>超凡攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D89" s="22" t="n">
@@ -7804,6 +8515,11 @@
       <c r="L89" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M89" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -7818,7 +8534,7 @@
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>超凡防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D90" s="21" t="n">
@@ -7856,6 +8572,11 @@
       <c r="L90" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M90" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -7870,7 +8591,7 @@
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>超凡生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D91" s="22" t="n">
@@ -7908,6 +8629,11 @@
       <c r="L91" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M91" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -7922,7 +8648,7 @@
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>超凡直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D92" s="21" t="n">
@@ -7960,6 +8686,11 @@
       <c r="L92" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M92" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -7974,7 +8705,7 @@
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>超凡护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D93" s="22" t="n">
@@ -8012,6 +8743,11 @@
       <c r="L93" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M93" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8762,7 @@
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>超凡治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D94" s="21" t="n">
@@ -8064,6 +8800,11 @@
       <c r="L94" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M94" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8819,7 @@
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>超凡反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D95" s="22" t="n">
@@ -8116,6 +8857,11 @@
       <c r="L95" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M95" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8876,7 @@
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>超凡火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D96" s="21" t="n">
@@ -8168,6 +8914,11 @@
       <c r="L96" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M96" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8933,7 @@
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>超凡持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D97" s="22" t="n">
@@ -8220,6 +8971,11 @@
       <c r="L97" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M97" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8990,7 @@
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>超凡冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D98" s="21" t="n">
@@ -8272,6 +9028,11 @@
       <c r="L98" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M98" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -8286,7 +9047,7 @@
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>超凡雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
@@ -8324,6 +9085,11 @@
       <c r="L99" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M99" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -8338,7 +9104,7 @@
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>天界攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D100" s="21" t="n">
@@ -8376,6 +9142,11 @@
       <c r="L100" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M100" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -8390,7 +9161,7 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>天界防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D101" s="22" t="n">
@@ -8428,6 +9199,11 @@
       <c r="L101" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M101" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -8442,7 +9218,7 @@
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>天界生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D102" s="21" t="n">
@@ -8480,6 +9256,11 @@
       <c r="L102" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M102" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -8494,7 +9275,7 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>天界攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D103" s="22" t="n">
@@ -8532,6 +9313,11 @@
       <c r="L103" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M103" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -8546,7 +9332,7 @@
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>天界防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D104" s="21" t="n">
@@ -8584,6 +9370,11 @@
       <c r="L104" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M104" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -8598,7 +9389,7 @@
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>天界生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D105" s="22" t="n">
@@ -8636,6 +9427,11 @@
       <c r="L105" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M105" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -8650,7 +9446,7 @@
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>天界直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D106" s="21" t="n">
@@ -8688,6 +9484,11 @@
       <c r="L106" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M106" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -8702,7 +9503,7 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>天界护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D107" s="22" t="n">
@@ -8740,6 +9541,11 @@
       <c r="L107" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M107" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -8754,7 +9560,7 @@
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>天界治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D108" s="21" t="n">
@@ -8792,6 +9598,11 @@
       <c r="L108" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M108" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -8806,7 +9617,7 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>天界反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D109" s="22" t="n">
@@ -8844,6 +9655,11 @@
       <c r="L109" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M109" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -8858,7 +9674,7 @@
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>天界火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D110" s="21" t="n">
@@ -8896,6 +9712,11 @@
       <c r="L110" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M110" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -8910,7 +9731,7 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>天界持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D111" s="22" t="n">
@@ -8948,6 +9769,11 @@
       <c r="L111" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M111" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -8962,7 +9788,7 @@
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>天界冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D112" s="21" t="n">
@@ -9000,6 +9826,11 @@
       <c r="L112" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M112" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9845,7 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>天界雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D113" s="22" t="n">
@@ -9052,6 +9883,11 @@
       <c r="L113" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M113" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9902,7 @@
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>登神攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D114" s="21" t="n">
@@ -9104,6 +9940,11 @@
       <c r="L114" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M114" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9959,7 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>登神防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D115" s="22" t="n">
@@ -9156,6 +9997,11 @@
       <c r="L115" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M115" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -9170,7 +10016,7 @@
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>登神生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D116" s="21" t="n">
@@ -9208,6 +10054,11 @@
       <c r="L116" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M116" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -9222,7 +10073,7 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>登神攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D117" s="22" t="n">
@@ -9260,6 +10111,11 @@
       <c r="L117" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M117" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -9274,7 +10130,7 @@
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>登神防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D118" s="21" t="n">
@@ -9312,6 +10168,11 @@
       <c r="L118" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M118" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -9326,7 +10187,7 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>登神生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
@@ -9364,6 +10225,11 @@
       <c r="L119" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M119" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -9378,7 +10244,7 @@
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>登神直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D120" s="21" t="n">
@@ -9416,6 +10282,11 @@
       <c r="L120" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M120" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -9430,7 +10301,7 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>登神护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
@@ -9468,6 +10339,11 @@
       <c r="L121" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M121" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -9482,7 +10358,7 @@
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>登神治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D122" s="21" t="n">
@@ -9520,6 +10396,11 @@
       <c r="L122" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M122" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -9534,7 +10415,7 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>登神反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D123" s="22" t="n">
@@ -9572,6 +10453,11 @@
       <c r="L123" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M123" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -9586,7 +10472,7 @@
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>登神火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D124" s="21" t="n">
@@ -9624,6 +10510,11 @@
       <c r="L124" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M124" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -9638,7 +10529,7 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>登神持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D125" s="22" t="n">
@@ -9676,6 +10567,11 @@
       <c r="L125" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M125" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -9690,7 +10586,7 @@
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>登神冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D126" s="21" t="n">
@@ -9728,6 +10624,11 @@
       <c r="L126" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M126" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -9742,7 +10643,7 @@
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>登神雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D127" s="22" t="n">
@@ -9780,6 +10681,11 @@
       <c r="L127" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M127" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
         </is>
       </c>
     </row>
@@ -9794,7 +10700,7 @@
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>宇宙攻击宝石</t>
+          <t>攻击宝石</t>
         </is>
       </c>
       <c r="D128" s="21" t="n">
@@ -9832,6 +10738,11 @@
       <c r="L128" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M128" s="37" t="inlineStr">
+        <is>
+          <t>Attack Gem</t>
         </is>
       </c>
     </row>
@@ -9846,7 +10757,7 @@
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>宇宙防御宝石</t>
+          <t>防御宝石</t>
         </is>
       </c>
       <c r="D129" s="22" t="n">
@@ -9884,6 +10795,11 @@
       <c r="L129" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M129" s="37" t="inlineStr">
+        <is>
+          <t>Guard Gem</t>
         </is>
       </c>
     </row>
@@ -9898,7 +10814,7 @@
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>宇宙生命宝石</t>
+          <t>气血宝石</t>
         </is>
       </c>
       <c r="D130" s="21" t="n">
@@ -9936,6 +10852,11 @@
       <c r="L130" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M130" s="37" t="inlineStr">
+        <is>
+          <t>HP Gem</t>
         </is>
       </c>
     </row>
@@ -9950,7 +10871,7 @@
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>宇宙攻击百分比宝石</t>
+          <t>强攻宝石</t>
         </is>
       </c>
       <c r="D131" s="22" t="n">
@@ -9988,6 +10909,11 @@
       <c r="L131" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M131" s="37" t="inlineStr">
+        <is>
+          <t>Might Gem</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10928,7 @@
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>宇宙防御百分比宝石</t>
+          <t>坚守宝石</t>
         </is>
       </c>
       <c r="D132" s="21" t="n">
@@ -10040,6 +10966,11 @@
       <c r="L132" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M132" s="37" t="inlineStr">
+        <is>
+          <t>Ward Gem</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10985,7 @@
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>宇宙生命百分比宝石</t>
+          <t>强体宝石</t>
         </is>
       </c>
       <c r="D133" s="22" t="n">
@@ -10092,6 +11023,11 @@
       <c r="L133" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M133" s="37" t="inlineStr">
+        <is>
+          <t>Vital Gem</t>
         </is>
       </c>
     </row>
@@ -10106,7 +11042,7 @@
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>宇宙直接伤害宝石</t>
+          <t>物伤宝石</t>
         </is>
       </c>
       <c r="D134" s="21" t="n">
@@ -10144,6 +11080,11 @@
       <c r="L134" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M134" s="37" t="inlineStr">
+        <is>
+          <t>Strike Gem</t>
         </is>
       </c>
     </row>
@@ -10158,7 +11099,7 @@
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>宇宙护甲获得量宝石</t>
+          <t>护甲宝石</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
@@ -10196,6 +11137,11 @@
       <c r="L135" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M135" s="37" t="inlineStr">
+        <is>
+          <t>Armor Gem</t>
         </is>
       </c>
     </row>
@@ -10210,7 +11156,7 @@
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>宇宙治疗效果宝石</t>
+          <t>治疗宝石</t>
         </is>
       </c>
       <c r="D136" s="21" t="n">
@@ -10248,6 +11194,11 @@
       <c r="L136" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M136" s="37" t="inlineStr">
+        <is>
+          <t>Heal Gem</t>
         </is>
       </c>
     </row>
@@ -10262,7 +11213,7 @@
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>宇宙反击伤害宝石</t>
+          <t>反击宝石</t>
         </is>
       </c>
       <c r="D137" s="22" t="n">
@@ -10300,6 +11251,11 @@
       <c r="L137" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M137" s="37" t="inlineStr">
+        <is>
+          <t>Counter Gem</t>
         </is>
       </c>
     </row>
@@ -10314,7 +11270,7 @@
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>宇宙火焰伤害宝石</t>
+          <t>火焰宝石</t>
         </is>
       </c>
       <c r="D138" s="21" t="n">
@@ -10352,6 +11308,11 @@
       <c r="L138" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M138" s="37" t="inlineStr">
+        <is>
+          <t>Fire Gem</t>
         </is>
       </c>
     </row>
@@ -10366,7 +11327,7 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>宇宙持续伤害宝石</t>
+          <t>持续伤害宝石</t>
         </is>
       </c>
       <c r="D139" s="22" t="n">
@@ -10404,6 +11365,11 @@
       <c r="L139" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M139" s="37" t="inlineStr">
+        <is>
+          <t>DoT Gem</t>
         </is>
       </c>
     </row>
@@ -10418,7 +11384,7 @@
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>宇宙冰霜伤害宝石</t>
+          <t>冰霜宝石</t>
         </is>
       </c>
       <c r="D140" s="21" t="n">
@@ -10456,6 +11422,11 @@
       <c r="L140" s="20" t="inlineStr">
         <is>
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
+        </is>
+      </c>
+      <c r="M140" s="37" t="inlineStr">
+        <is>
+          <t>Frost Gem</t>
         </is>
       </c>
     </row>
@@ -10470,7 +11441,7 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>宇宙雷击伤害宝石</t>
+          <t>雷电宝石</t>
         </is>
       </c>
       <c r="D141" s="22" t="n">
@@ -10510,16 +11481,21 @@
           <t>一致（仅目录源码数值；战斗与显示按专项验收）</t>
         </is>
       </c>
+      <c r="M141" s="37" t="inlineStr">
+        <is>
+          <t>Storm Gem</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L141"/>
+  <autoFilter ref="A1:M141"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
@@ -10940,14 +11916,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10964,6 +11940,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -11037,6 +12016,21 @@
           <t>当前核对状态</t>
         </is>
       </c>
+      <c r="O1" s="36" t="inlineStr">
+        <is>
+          <t>英文名称</t>
+        </is>
+      </c>
+      <c r="P1" s="36" t="inlineStr">
+        <is>
+          <t>英文套装</t>
+        </is>
+      </c>
+      <c r="Q1" s="36" t="inlineStr">
+        <is>
+          <t>英文部位</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="29" customHeight="1">
       <c r="A2" s="21" t="n">
@@ -11097,6 +12091,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O2" s="37" t="inlineStr">
+        <is>
+          <t>War Weapon</t>
+        </is>
+      </c>
+      <c r="P2" s="37" t="inlineStr">
+        <is>
+          <t>War</t>
+        </is>
+      </c>
+      <c r="Q2" s="37" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="29" customHeight="1">
       <c r="A3" s="22" t="n">
@@ -11157,6 +12166,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O3" s="37" t="inlineStr">
+        <is>
+          <t>War Helm</t>
+        </is>
+      </c>
+      <c r="P3" s="37" t="inlineStr">
+        <is>
+          <t>War</t>
+        </is>
+      </c>
+      <c r="Q3" s="37" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" s="21" t="n">
@@ -11217,6 +12241,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>War Armor</t>
+        </is>
+      </c>
+      <c r="P4" s="37" t="inlineStr">
+        <is>
+          <t>War</t>
+        </is>
+      </c>
+      <c r="Q4" s="37" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="22" t="n">
@@ -11277,6 +12316,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O5" s="37" t="inlineStr">
+        <is>
+          <t>War Belt</t>
+        </is>
+      </c>
+      <c r="P5" s="37" t="inlineStr">
+        <is>
+          <t>War</t>
+        </is>
+      </c>
+      <c r="Q5" s="37" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="29" customHeight="1">
       <c r="A6" s="21" t="n">
@@ -11337,6 +12391,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O6" s="37" t="inlineStr">
+        <is>
+          <t>War Boots</t>
+        </is>
+      </c>
+      <c r="P6" s="37" t="inlineStr">
+        <is>
+          <t>War</t>
+        </is>
+      </c>
+      <c r="Q6" s="37" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="22" t="n">
@@ -11397,6 +12466,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O7" s="37" t="inlineStr">
+        <is>
+          <t>War Accessory</t>
+        </is>
+      </c>
+      <c r="P7" s="37" t="inlineStr">
+        <is>
+          <t>War</t>
+        </is>
+      </c>
+      <c r="Q7" s="37" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="21" t="n">
@@ -11457,6 +12541,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O8" s="37" t="inlineStr">
+        <is>
+          <t>Iron Weapon</t>
+        </is>
+      </c>
+      <c r="P8" s="37" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="Q8" s="37" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="A9" s="22" t="n">
@@ -11517,6 +12616,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O9" s="37" t="inlineStr">
+        <is>
+          <t>Iron Helm</t>
+        </is>
+      </c>
+      <c r="P9" s="37" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="Q9" s="37" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" s="21" t="n">
@@ -11577,6 +12691,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O10" s="37" t="inlineStr">
+        <is>
+          <t>Iron Armor</t>
+        </is>
+      </c>
+      <c r="P10" s="37" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="Q10" s="37" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="29" customHeight="1">
       <c r="A11" s="22" t="n">
@@ -11637,6 +12766,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O11" s="37" t="inlineStr">
+        <is>
+          <t>Iron Belt</t>
+        </is>
+      </c>
+      <c r="P11" s="37" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="Q11" s="37" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="29" customHeight="1">
       <c r="A12" s="21" t="n">
@@ -11697,6 +12841,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O12" s="37" t="inlineStr">
+        <is>
+          <t>Iron Boots</t>
+        </is>
+      </c>
+      <c r="P12" s="37" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="Q12" s="37" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="29" customHeight="1">
       <c r="A13" s="22" t="n">
@@ -11757,6 +12916,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O13" s="37" t="inlineStr">
+        <is>
+          <t>Iron Accessory</t>
+        </is>
+      </c>
+      <c r="P13" s="37" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="Q13" s="37" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="29" customHeight="1">
       <c r="A14" s="21" t="n">
@@ -11817,6 +12991,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O14" s="37" t="inlineStr">
+        <is>
+          <t>Herb Weapon</t>
+        </is>
+      </c>
+      <c r="P14" s="37" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="Q14" s="37" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="29" customHeight="1">
       <c r="A15" s="22" t="n">
@@ -11877,6 +13066,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O15" s="37" t="inlineStr">
+        <is>
+          <t>Herb Helm</t>
+        </is>
+      </c>
+      <c r="P15" s="37" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="Q15" s="37" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="29" customHeight="1">
       <c r="A16" s="21" t="n">
@@ -11937,6 +13141,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O16" s="37" t="inlineStr">
+        <is>
+          <t>Herb Armor</t>
+        </is>
+      </c>
+      <c r="P16" s="37" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="Q16" s="37" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="29" customHeight="1">
       <c r="A17" s="22" t="n">
@@ -11997,6 +13216,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O17" s="37" t="inlineStr">
+        <is>
+          <t>Herb Belt</t>
+        </is>
+      </c>
+      <c r="P17" s="37" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="Q17" s="37" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="29" customHeight="1">
       <c r="A18" s="21" t="n">
@@ -12057,6 +13291,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O18" s="37" t="inlineStr">
+        <is>
+          <t>Herb Boots</t>
+        </is>
+      </c>
+      <c r="P18" s="37" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="Q18" s="37" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="29" customHeight="1">
       <c r="A19" s="22" t="n">
@@ -12117,6 +13366,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O19" s="37" t="inlineStr">
+        <is>
+          <t>Herb Accessory</t>
+        </is>
+      </c>
+      <c r="P19" s="37" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="Q19" s="37" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="29" customHeight="1">
       <c r="A20" s="21" t="n">
@@ -12177,6 +13441,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O20" s="37" t="inlineStr">
+        <is>
+          <t>Wind Weapon</t>
+        </is>
+      </c>
+      <c r="P20" s="37" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="Q20" s="37" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="29" customHeight="1">
       <c r="A21" s="22" t="n">
@@ -12237,6 +13516,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O21" s="37" t="inlineStr">
+        <is>
+          <t>Wind Helm</t>
+        </is>
+      </c>
+      <c r="P21" s="37" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="Q21" s="37" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="29" customHeight="1">
       <c r="A22" s="21" t="n">
@@ -12297,6 +13591,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O22" s="37" t="inlineStr">
+        <is>
+          <t>Wind Armor</t>
+        </is>
+      </c>
+      <c r="P22" s="37" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="Q22" s="37" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="29" customHeight="1">
       <c r="A23" s="22" t="n">
@@ -12357,6 +13666,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O23" s="37" t="inlineStr">
+        <is>
+          <t>Wind Belt</t>
+        </is>
+      </c>
+      <c r="P23" s="37" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="Q23" s="37" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="29" customHeight="1">
       <c r="A24" s="21" t="n">
@@ -12417,6 +13741,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O24" s="37" t="inlineStr">
+        <is>
+          <t>Wind Boots</t>
+        </is>
+      </c>
+      <c r="P24" s="37" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="Q24" s="37" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="29" customHeight="1">
       <c r="A25" s="22" t="n">
@@ -12477,6 +13816,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O25" s="37" t="inlineStr">
+        <is>
+          <t>Wind Accessory</t>
+        </is>
+      </c>
+      <c r="P25" s="37" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="Q25" s="37" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="29" customHeight="1">
       <c r="A26" s="21" t="n">
@@ -12537,6 +13891,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O26" s="37" t="inlineStr">
+        <is>
+          <t>Bone Weapon</t>
+        </is>
+      </c>
+      <c r="P26" s="37" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="Q26" s="37" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="29" customHeight="1">
       <c r="A27" s="22" t="n">
@@ -12597,6 +13966,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O27" s="37" t="inlineStr">
+        <is>
+          <t>Bone Helm</t>
+        </is>
+      </c>
+      <c r="P27" s="37" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="Q27" s="37" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="29" customHeight="1">
       <c r="A28" s="21" t="n">
@@ -12657,6 +14041,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O28" s="37" t="inlineStr">
+        <is>
+          <t>Bone Armor</t>
+        </is>
+      </c>
+      <c r="P28" s="37" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="Q28" s="37" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="29" customHeight="1">
       <c r="A29" s="22" t="n">
@@ -12717,6 +14116,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O29" s="37" t="inlineStr">
+        <is>
+          <t>Bone Belt</t>
+        </is>
+      </c>
+      <c r="P29" s="37" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="Q29" s="37" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="29" customHeight="1">
       <c r="A30" s="21" t="n">
@@ -12777,6 +14191,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O30" s="37" t="inlineStr">
+        <is>
+          <t>Bone Boots</t>
+        </is>
+      </c>
+      <c r="P30" s="37" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="Q30" s="37" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="29" customHeight="1">
       <c r="A31" s="22" t="n">
@@ -12837,6 +14266,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O31" s="37" t="inlineStr">
+        <is>
+          <t>Bone Accessory</t>
+        </is>
+      </c>
+      <c r="P31" s="37" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="Q31" s="37" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="29" customHeight="1">
       <c r="A32" s="21" t="n">
@@ -12897,6 +14341,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O32" s="37" t="inlineStr">
+        <is>
+          <t>Mountain Weapon</t>
+        </is>
+      </c>
+      <c r="P32" s="37" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="Q32" s="37" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="29" customHeight="1">
       <c r="A33" s="22" t="n">
@@ -12957,6 +14416,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O33" s="37" t="inlineStr">
+        <is>
+          <t>Mountain Helm</t>
+        </is>
+      </c>
+      <c r="P33" s="37" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="Q33" s="37" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="29" customHeight="1">
       <c r="A34" s="21" t="n">
@@ -13017,6 +14491,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O34" s="37" t="inlineStr">
+        <is>
+          <t>Mountain Armor</t>
+        </is>
+      </c>
+      <c r="P34" s="37" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="Q34" s="37" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="29" customHeight="1">
       <c r="A35" s="22" t="n">
@@ -13077,6 +14566,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O35" s="37" t="inlineStr">
+        <is>
+          <t>Mountain Belt</t>
+        </is>
+      </c>
+      <c r="P35" s="37" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="Q35" s="37" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="29" customHeight="1">
       <c r="A36" s="21" t="n">
@@ -13137,6 +14641,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O36" s="37" t="inlineStr">
+        <is>
+          <t>Mountain Boots</t>
+        </is>
+      </c>
+      <c r="P36" s="37" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="Q36" s="37" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="29" customHeight="1">
       <c r="A37" s="22" t="n">
@@ -13197,6 +14716,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O37" s="37" t="inlineStr">
+        <is>
+          <t>Mountain Accessory</t>
+        </is>
+      </c>
+      <c r="P37" s="37" t="inlineStr">
+        <is>
+          <t>Mountain</t>
+        </is>
+      </c>
+      <c r="Q37" s="37" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="29" customHeight="1">
       <c r="A38" s="21" t="n">
@@ -13257,6 +14791,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O38" s="37" t="inlineStr">
+        <is>
+          <t>Basic Weapon</t>
+        </is>
+      </c>
+      <c r="P38" s="37" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="Q38" s="37" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="29" customHeight="1">
       <c r="A39" s="22" t="n">
@@ -13317,6 +14866,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O39" s="37" t="inlineStr">
+        <is>
+          <t>Basic Helm</t>
+        </is>
+      </c>
+      <c r="P39" s="37" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="Q39" s="37" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="29" customHeight="1">
       <c r="A40" s="21" t="n">
@@ -13377,6 +14941,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O40" s="37" t="inlineStr">
+        <is>
+          <t>Basic Armor</t>
+        </is>
+      </c>
+      <c r="P40" s="37" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="Q40" s="37" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="29" customHeight="1">
       <c r="A41" s="22" t="n">
@@ -13437,6 +15016,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O41" s="37" t="inlineStr">
+        <is>
+          <t>Basic Belt</t>
+        </is>
+      </c>
+      <c r="P41" s="37" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="Q41" s="37" t="inlineStr">
+        <is>
+          <t>Belt</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="29" customHeight="1">
       <c r="A42" s="21" t="n">
@@ -13497,6 +15091,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O42" s="37" t="inlineStr">
+        <is>
+          <t>Basic Boots</t>
+        </is>
+      </c>
+      <c r="P42" s="37" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="Q42" s="37" t="inlineStr">
+        <is>
+          <t>Boots</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="29" customHeight="1">
       <c r="A43" s="22" t="n">
@@ -13557,6 +15166,21 @@
           <t>模板名称已核对；批准减半设计仍待落实</t>
         </is>
       </c>
+      <c r="O43" s="37" t="inlineStr">
+        <is>
+          <t>Basic Accessory</t>
+        </is>
+      </c>
+      <c r="P43" s="37" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="Q43" s="37" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="29" customHeight="1">
       <c r="A44" s="21" t="n">
@@ -13619,6 +15243,11 @@
           <t>旧档兼容；内力快照不增加有效内力</t>
         </is>
       </c>
+      <c r="O44" s="37" t="inlineStr">
+        <is>
+          <t>Plain Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="29" customHeight="1">
       <c r="A45" s="22" t="n">
@@ -13681,6 +15310,11 @@
           <t>旧档兼容；内力快照不增加有效内力</t>
         </is>
       </c>
+      <c r="O45" s="37" t="inlineStr">
+        <is>
+          <t>Plain Armor</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="29" customHeight="1">
       <c r="A46" s="21" t="n">
@@ -13743,6 +15377,11 @@
           <t>旧档兼容；内力快照不增加有效内力</t>
         </is>
       </c>
+      <c r="O46" s="37" t="inlineStr">
+        <is>
+          <t>Plain Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="29" customHeight="1">
       <c r="A47" s="22" t="n">
@@ -13805,6 +15444,11 @@
           <t>旧档兼容；内力快照不增加有效内力</t>
         </is>
       </c>
+      <c r="O47" s="37" t="inlineStr">
+        <is>
+          <t>Plain Accessory</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="29" customHeight="1">
       <c r="A48" s="21" t="n">
@@ -13867,6 +15511,11 @@
           <t>旧档兼容；内力快照不增加有效内力</t>
         </is>
       </c>
+      <c r="O48" s="37" t="inlineStr">
+        <is>
+          <t>Plain Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="29" customHeight="1">
       <c r="A49" s="22" t="n">
@@ -13929,6 +15578,11 @@
           <t>旧档兼容；内力快照不增加有效内力</t>
         </is>
       </c>
+      <c r="O49" s="37" t="inlineStr">
+        <is>
+          <t>Plain Armor</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="29" customHeight="1">
       <c r="A50" s="21" t="n">
@@ -13991,16 +15645,21 @@
           <t>旧档兼容；内力快照不增加有效内力</t>
         </is>
       </c>
+      <c r="O50" s="37" t="inlineStr">
+        <is>
+          <t>Plain Accessory</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N50"/>
+  <autoFilter ref="A1:Q50"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B8B68"/>
@@ -14177,7 +15836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
@@ -15252,7 +16911,1946 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00244D57"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="70" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>当前装备提示的效果文本</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>当前运行时状态</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>生成状态</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>现行触发/作用域</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>本轮审查处理</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>当前数据单位</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>稳定词缀ID</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>源码定位</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>英文短名</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>英文效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="54" customHeight="1">
+      <c r="A2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>气血 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>已接入装备属性投影</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>通用随机池</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>按穿戴者汇总到装备属性预算</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>本轮分系审查不自动改动通用属性</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Affix.Universal.MaxHealth</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:59
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="54" customHeight="1">
+      <c r="A3" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>攻击 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>已接入装备属性投影</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>通用随机池</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>按穿戴者汇总到装备属性预算</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>本轮分系审查不自动改动通用属性</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Affix.Universal.Attack</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:60
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="54" customHeight="1">
+      <c r="A4" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>防御 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>已接入装备属性投影</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>通用随机池</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>按穿戴者汇总到装备属性预算</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>本轮分系审查不自动改动通用属性</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Affix.Universal.Defense</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:61
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>历史兼容</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>内力上限加成（已停用，当前提示不显示）</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>已停用：有效内力贡献为0</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>旧档兼容，不进入新随机池</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>属性投影忽略；统一装备提示不显示</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>保留旧档解析，不进入新随机池</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Affix.Universal.MaxMana</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:70
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>历史兼容</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>速度 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>历史兼容属性投影</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>旧档兼容，不进入新随机池</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>仅旧实例兼容；不进入新随机池</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>保留旧档解析和迁出路径</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Affix.Universal.Speed</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:71
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>破军</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>直接伤害 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>补接结算</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Affix.PoJun.DirectDamage</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:83
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>破军</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>多段伤害 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>先定义多段，再接入</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Affix.PoJun.MultiHitDamage</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:84
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>破军</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>破甲层数 +{数值}</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>重设效果含义</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Affix.PoJun.ArmorBreakStacks</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:85
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>破军</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>对破绽目标的伤害 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>统一术语并补接</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Affix.PoJun.VulnerableTargetDamage</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:86
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>破军</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>每回合首次攻击伤害 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>明确首次计数</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Affix.PoJun.FirstAttackDamage</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:87
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>玄甲</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>护甲获得量 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>已接入产甲增幅（源码核对）</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>按护甲产生者匹配；调用方允许放大时生效</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>已接入75%边际模型</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>Affix.XuanJia.ArmorGain</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:91
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>玄甲</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>护甲保留比例 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>补接并定义合并规则</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Affix.XuanJia.ArmorRetention</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:92
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>玄甲</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>反击伤害 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>补接反应伤害入口</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>Affix.XuanJia.CounterDamage</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:93
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1">
+      <c r="A15" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>玄甲</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>援护减伤 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>明确承伤对象</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Affix.XuanJia.GuardReduction</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:94
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1">
+      <c r="A16" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>玄甲</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>低气血防护 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>重设低血保护定义</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Affix.XuanJia.LowHealthProtection</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:95
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>青囊</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>治疗量 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>补接治疗计算</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Affix.QingNang.Healing</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:99
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>青囊</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>净化加成 +{数值}</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>优先重设计</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Affix.QingNang.Cleanse</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:100
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>青囊</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>溢出治疗转化比例 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>明确转换目标</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Affix.QingNang.OverhealConversion</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:101
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>青囊</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>内力恢复量 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>补接回复，维持固定上限</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>Affix.QingNang.ManaRecovery</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:102
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>青囊</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>低气血治疗量 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>明确低血治疗条件</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Affix.QingNang.EmergencyHealing</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:103
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>追风</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>抽牌数量 +{数值}</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>已退休；旧战斗快照兼容至结算</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>不再生成或洗炼；旧装备载入时转换</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>原资源操作不接入；改为未占用数值词缀</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>定向迁移；省力优先转乘风；强化/孔/其他词条保留。docs/design/2026-09-11-affix-wind-ramp.md</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ZhuiFeng.Draw</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:107
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>追风</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>低费牌效果 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>重新确认玩法方向</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Affix.ZhuiFeng.LowCostBonus</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:108
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>追风</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>气力生成 +{数值}</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>已退休；旧战斗快照兼容至结算</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>不再生成或洗炼；旧装备载入时转换</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>原资源操作不接入；改为未占用数值词缀</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>定向迁移；省力优先转乘风；强化/孔/其他词条保留。docs/design/2026-09-11-affix-wind-ramp.md</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ZhuiFeng.SharedEnergy</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:109
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>追风</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>连击计数 +{数值}</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>已退休；旧战斗快照兼容至结算</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>不再生成或洗炼；旧装备载入时转换</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>原资源操作不接入；改为未占用数值词缀</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>定向迁移；省力优先转乘风；强化/孔/其他词条保留。docs/design/2026-09-11-affix-wind-ramp.md</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>Affix.ZhuiFeng.ComboCount</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:110
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>追风</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>临时费用减免 +{数值}</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>已退休；旧战斗快照兼容至结算</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>不再生成或洗炼；旧装备载入时转换</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>原资源操作不接入；改为未占用数值词缀</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>定向迁移；省力优先转乘风；强化/孔/其他词条保留。docs/design/2026-09-11-affix-wind-ramp.md</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ZhuiFeng.TemporaryCostReduction</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:111
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>蚀骨</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>施加中毒层数 +{数值}</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>补接并限制重复施加</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>Affix.ShiGu.Poison</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:115
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>蚀骨</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>施加流血层数 +{数值}</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>补接并限制重复施加</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ShiGu.Bleed</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:116
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>蚀骨</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>施加灼烧层数 +{数值}</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>补接并限制重复施加</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>Affix.ShiGu.Burn</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:117
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>蚀骨</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>持续伤害 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>明确伤害范围及归属</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ShiGu.DamageOverTime</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:118
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>蚀骨</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>保留状态层数 +{数值}</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>明确保留时机</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>Affix.ShiGu.StatusRetention</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:119
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>山河</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>地势效果 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>拆清地势收益类别</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ShanHe.TerrainPower</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:123
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>山河</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>地势牌费用减免 +{数值}</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>已退休；旧战斗快照兼容至结算</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>不再生成或洗炼；旧装备载入时转换</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>原资源操作不接入；改为未占用数值词缀</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>定向迁移；省力优先转乘风；强化/孔/其他词条保留。docs/design/2026-09-11-affix-wind-ramp.md</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>FlatCount</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>Affix.ShanHe.TerrainCostReduction</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:124
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>山河</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>相邻队友增益 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>优先重设效果</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ShanHe.AdjacentAllyPower</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:125
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>山河</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>阵型收益 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>优先重设效果</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>Affix.ShanHe.FormationPower</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:126
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>山河</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>全队地势增益 +{数值}%</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>未找到战斗数值消费者（源码核对）</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>对应套装随机池</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>修正团队作用域设计</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ShanHe.TeamTerrainPower</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:127
+Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>追风</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>每回合第3张起，自身牌直伤每张递增1%；全队计数，同名叠加，重放不计数。</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>真实伤害/生成/洗炼/旧档核心检查通过；实机Tooltip待复核</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>追风随机池；固定1%</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>穿戴者当前牌物理/元素直击；全队主动计数；每回合重置</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>1%=100基点；同名按条数加算，不套用0.5系数或75%递减</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>BasisPoints</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>Affix.ZhuiFeng.LateCardDamage</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>Source/GameXXK/Private/GameXXKCardRules.cpp | docs/design/2026-09-11-affix-wind-ramp.md</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Tailwind</t>
+        </is>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>From team card 3 each round: own direct card damage +1% per card. Copies stack; replays do not count.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L37"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16237,1874 +19835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00244D57"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="47" customWidth="1" min="9" max="9"/>
-    <col width="65" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>归属</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>当前装备提示的效果文本</t>
-        </is>
-      </c>
-      <c r="D1" s="12" t="inlineStr">
-        <is>
-          <t>当前运行时状态</t>
-        </is>
-      </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>生成状态</t>
-        </is>
-      </c>
-      <c r="F1" s="12" t="inlineStr">
-        <is>
-          <t>现行触发/作用域</t>
-        </is>
-      </c>
-      <c r="G1" s="12" t="inlineStr">
-        <is>
-          <t>本轮审查处理</t>
-        </is>
-      </c>
-      <c r="H1" s="12" t="inlineStr">
-        <is>
-          <t>当前数据单位</t>
-        </is>
-      </c>
-      <c r="I1" s="12" t="inlineStr">
-        <is>
-          <t>稳定词缀ID</t>
-        </is>
-      </c>
-      <c r="J1" s="12" t="inlineStr">
-        <is>
-          <t>源码定位</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="54" customHeight="1">
-      <c r="A2" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>气血 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D2" s="20" t="inlineStr">
-        <is>
-          <t>已接入装备属性投影</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>通用随机池</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>按穿戴者汇总到装备属性预算</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>本轮分系审查不自动改动通用属性</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>Affix.Universal.MaxHealth</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:59
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="54" customHeight="1">
-      <c r="A3" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>攻击 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>已接入装备属性投影</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>通用随机池</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>按穿戴者汇总到装备属性预算</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>本轮分系审查不自动改动通用属性</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I3" s="14" t="inlineStr">
-        <is>
-          <t>Affix.Universal.Attack</t>
-        </is>
-      </c>
-      <c r="J3" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:60
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>通用</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>防御 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>已接入装备属性投影</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>通用随机池</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>按穿戴者汇总到装备属性预算</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>本轮分系审查不自动改动通用属性</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>Affix.Universal.Defense</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:61
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>历史兼容</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>内力上限加成（已停用，当前提示不显示）</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>已停用：有效内力贡献为0</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>旧档兼容，不进入新随机池</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>属性投影忽略；统一装备提示不显示</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>保留旧档解析，不进入新随机池</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>Affix.Universal.MaxMana</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:70
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>历史兼容</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>速度 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>历史兼容属性投影</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>旧档兼容，不进入新随机池</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>仅旧实例兼容；不进入新随机池</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>保留旧档解析和迁出路径</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>Affix.Universal.Speed</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:71
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>破军</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>直接伤害 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>补接结算</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>Affix.PoJun.DirectDamage</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:83
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>破军</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>多段伤害 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>先定义多段，再接入</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>Affix.PoJun.MultiHitDamage</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:84
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>破军</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>破甲层数 +{数值}</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>重设效果含义</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Affix.PoJun.ArmorBreakStacks</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:85
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>破军</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>对破绽目标的伤害 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>统一术语并补接</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>Affix.PoJun.VulnerableTargetDamage</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:86
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>破军</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>每回合首次攻击伤害 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>明确首次计数</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Affix.PoJun.FirstAttackDamage</t>
-        </is>
-      </c>
-      <c r="J11" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:87
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>玄甲</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>护甲获得量 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>已接入产甲增幅（源码核对）</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>按护甲产生者匹配；调用方允许放大时生效</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>已接入75%边际模型</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>Affix.XuanJia.ArmorGain</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:91
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>玄甲</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>护甲保留比例 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>补接并定义合并规则</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>Affix.XuanJia.ArmorRetention</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:92
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>玄甲</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>反击伤害 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>补接反应伤害入口</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>Affix.XuanJia.CounterDamage</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:93
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="54" customHeight="1">
-      <c r="A15" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>玄甲</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>援护减伤 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>明确承伤对象</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>Affix.XuanJia.GuardReduction</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:94
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="54" customHeight="1">
-      <c r="A16" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>玄甲</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>低气血防护 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>重设低血保护定义</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>Affix.XuanJia.LowHealthProtection</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:95
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="54" customHeight="1">
-      <c r="A17" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>青囊</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>治疗量 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>补接治疗计算</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>Affix.QingNang.Healing</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:99
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>青囊</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>净化加成 +{数值}</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>优先重设计</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>Affix.QingNang.Cleanse</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:100
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>青囊</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>溢出治疗转化比例 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>明确转换目标</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>Affix.QingNang.OverhealConversion</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:101
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>青囊</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>内力恢复量 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>补接回复，维持固定上限</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>Affix.QingNang.ManaRecovery</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:102
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="54" customHeight="1">
-      <c r="A21" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>青囊</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>低气血治疗量 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>明确低血治疗条件</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>Affix.QingNang.EmergencyHealing</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:103
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="54" customHeight="1">
-      <c r="A22" s="21" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>追风</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>抽牌数量 +{数值}</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>重设计为有界触发</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ZhuiFeng.Draw</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:107
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>追风</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>低费牌效果 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>重新确认玩法方向</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>Affix.ZhuiFeng.LowCostBonus</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:108
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="21" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>追风</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>气力生成 +{数值}</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>重设计为有界触发</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ZhuiFeng.SharedEnergy</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:109
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>追风</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>连击计数 +{数值}</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>替换虚拟计数收益</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>Affix.ZhuiFeng.ComboCount</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:110
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="21" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>追风</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>临时费用减免 +{数值}</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>明确支付前减费</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ZhuiFeng.TemporaryCostReduction</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:111
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>蚀骨</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>施加中毒层数 +{数值}</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>补接并限制重复施加</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>Affix.ShiGu.Poison</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:115
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="54" customHeight="1">
-      <c r="A28" s="21" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>蚀骨</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>施加流血层数 +{数值}</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>补接并限制重复施加</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ShiGu.Bleed</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:116
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="54" customHeight="1">
-      <c r="A29" s="22" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>蚀骨</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>施加灼烧层数 +{数值}</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>补接并限制重复施加</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>Affix.ShiGu.Burn</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:117
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="54" customHeight="1">
-      <c r="A30" s="21" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>蚀骨</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>持续伤害 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>明确伤害范围及归属</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ShiGu.DamageOverTime</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:118
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="54" customHeight="1">
-      <c r="A31" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>蚀骨</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>保留状态层数 +{数值}</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>明确保留时机</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>Affix.ShiGu.StatusRetention</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:119
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="21" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>山河</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>地势效果 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>拆清地势收益类别</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ShanHe.TerrainPower</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:123
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="54" customHeight="1">
-      <c r="A33" s="22" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>山河</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>地势牌费用减免 +{数值}</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>明确与套装减费关系</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>FlatCount</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>Affix.ShanHe.TerrainCostReduction</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:124
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="54" customHeight="1">
-      <c r="A34" s="21" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>山河</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>相邻队友增益 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>优先重设效果</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ShanHe.AdjacentAllyPower</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:125
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="54" customHeight="1">
-      <c r="A35" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>山河</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>阵型收益 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>优先重设效果</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>Affix.ShanHe.FormationPower</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:126
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="54" customHeight="1">
-      <c r="A36" s="21" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>山河</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>全队地势增益 +{数值}%</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>对应套装随机池</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="inlineStr">
-        <is>
-          <t>当前仅Owner/Passive描述符；实际触发尚未接入</t>
-        </is>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>修正团队作用域设计</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>BasisPoints</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>Affix.ShanHe.TeamTerrainPower</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp:127
-Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J36"/>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D99A33"/>
@@ -18438,7 +20169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D99A33"/>
@@ -18770,7 +20501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D99A33"/>
@@ -19225,7 +20956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
@@ -19843,7 +21574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
@@ -20177,7 +21908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00244D57"/>
@@ -20421,7 +22152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20757,7 +22488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21383,7 +23114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22148,7 +23879,7 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
+          <t>退休，不再接入旧资源效果</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -22163,12 +23894,12 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>优先小整数收益与限次，不能把六件合计36张再简单减半。</t>
+          <t>旧档转换为未占用数值项，保留品质/数值相对位置</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>叠加模型已记录；本词缀仍待触发定义与运行时接入</t>
+          <t>用户已确认；转换与运行时测试中</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -22239,7 +23970,7 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
+          <t>退休，不再接入旧资源效果</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -22254,12 +23985,12 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>优先每次1气与严格限次；不直接读取1～10气的通用整数区间。</t>
+          <t>旧档转换为未占用数值项，保留品质/数值相对位置</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>叠加模型已记录；本词缀仍待触发定义与运行时接入</t>
+          <t>用户已确认；转换与运行时测试中</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -22284,7 +24015,7 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
+          <t>退休，不再接入旧资源效果</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -22299,12 +24030,12 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>新收益待定；旧连击计数不直接接入全队计数器。</t>
+          <t>旧档转换为未占用数值项，保留品质/数值相对位置</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>叠加模型已记录；本词缀仍待触发定义与运行时接入</t>
+          <t>用户已确认；转换与运行时测试中</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
@@ -22329,7 +24060,7 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
+          <t>退休，不再接入旧资源效果</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -22344,12 +24075,12 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>优先每次少耗1气与限次，最低费用0。</t>
+          <t>旧档转换为未占用数值项，保留品质/数值相对位置</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>叠加模型已记录；本词缀仍待触发定义与运行时接入</t>
+          <t>用户已确认；转换与运行时测试中</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -22646,7 +24377,7 @@
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>未找到战斗数值消费者（源码核对）</t>
+          <t>退休，不再接入旧资源效果</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -22661,12 +24392,12 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>优先每次少耗1气与限次；是否另选触发张数待定。</t>
+          <t>旧档转换为未占用数值项，保留品质/数值相对位置</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>叠加模型已记录；本词缀仍待触发定义与运行时接入</t>
+          <t>用户已确认；转换与运行时测试中</t>
         </is>
       </c>
       <c r="I28" s="13" t="inlineStr">
@@ -22810,6 +24541,51 @@
       <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Affix.ShanHe.TeamTerrainPower</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>追风</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>每回合第3张起，自身牌直伤每张递增1%；全队计数，同名叠加，重放不计数。</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="inlineStr">
+        <is>
+          <t>已接入；实际伤害矩阵通过</t>
+        </is>
+      </c>
+      <c r="E32" s="38" t="inlineStr">
+        <is>
+          <t>全队第3张起；穿戴者自己的当前牌</t>
+        </is>
+      </c>
+      <c r="F32" s="38" t="inlineStr">
+        <is>
+          <t>不增重放计数，不影响固定伤害/DOT/装备触发</t>
+        </is>
+      </c>
+      <c r="G32" s="38" t="inlineStr">
+        <is>
+          <t>固定1%；两条第3/4张分别+2%/+4%</t>
+        </is>
+      </c>
+      <c r="H32" s="38" t="inlineStr">
+        <is>
+          <t>核心5/5与相邻69/69</t>
+        </is>
+      </c>
+      <c r="I32" s="38" t="inlineStr">
+        <is>
+          <t>Affix.ZhuiFeng.LateCardDamage</t>
         </is>
       </c>
     </row>
@@ -22936,7 +24712,7 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -22975,7 +24751,7 @@
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23014,7 +24790,7 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23053,7 +24829,7 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23092,7 +24868,7 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23131,7 +24907,7 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23170,7 +24946,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23209,7 +24985,7 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23248,7 +25024,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23287,7 +25063,7 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>分系百分比先乘0.5，再按04D做75%上限的边际递减；本列是名义值。产甲已接入，其余29条仍待接入；整数类继续独立重设计。</t>
+          <t>产甲已接入递减；追风乘风各品质固定1%并线性叠加（不适用本页区间/折半）；其余分系项待接入，退休5项见04H。</t>
         </is>
       </c>
     </row>
@@ -23306,7 +25082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -23748,6 +25524,28 @@
       <c r="D20" s="13" t="inlineStr">
         <is>
           <t>已写入产甲结算与对应回归；实测证据见本轮验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>追风乘风例外</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>max(0,主动牌序号-2) × 同名条数 × 1%</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>固定1%直接叠加，不折半、不使用75%递减；详见04H</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>用户确认；实际出牌/叠加/回合检查通过</t>
         </is>
       </c>
     </row>
@@ -27586,212 +29384,325 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00244D57"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="67" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>入口</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>代码当前行为</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>名称状态</t>
-        </is>
-      </c>
-      <c r="D1" s="12" t="inlineStr">
-        <is>
-          <t>核对范围</t>
-        </is>
-      </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>源码定位</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="39" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>统一装备提示</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>使用ModifierLabel + 数值/百分比；最大内力词缀直接隐藏。</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>已直接描述效果</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>这是总表词缀名称的取值来源。</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/UI/GameXXKEquipmentTooltipPresentation.cpp:207</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="39" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>桌面背包装备格</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>调用统一装备提示Build/Bind。</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>已直接描述效果</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>当前默认桌面工作台入口。</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/UI/GameXXKDesktopTrainingWorkbenchWidget.cpp:6565</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="39" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>桌面商店结果卡</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>调用统一装备提示Build/Bind。</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>已直接描述效果</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>当前桌面商店购买结果入口。</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/UI/GameXXKDesktopTrainingWorkbenchWidget.cpp:4536</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="29" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>旧商店控件</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>仍有读取Affix-&gt;DisplayName的格式化代码。</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>仍保留旧短名路径</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>源码事实；本轮未验证旧控件在当前流程的可达性。</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/UI/GameXXKMetaShopWidget.cpp:132</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="29" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>旧伙伴名册控件</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>仍有读取Affix-&gt;DisplayName的格式化代码。</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>仍保留旧短名路径</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>源码事实；本轮未验证旧控件在当前流程的可达性。</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/UI/GameXXKCompanionRosterWidget.cpp:468</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="29" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>词缀目录内部字段</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>DisplayName仍保留旧别名；稳定ID用于实例和存档解析。</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>内部字段未改名</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>总表主名称不再采用旧别名；不把显示更新误写成C++字段已修改。</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Source/GameXXK/Private/GameXXKAffixCatalog.cpp</t>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>追风乘风 · 固定1%递增</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>用户裁决 2026-09-11；实现/测试进度见项目状态表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>中文规则</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="inlineStr">
+        <is>
+          <t>每回合第3张起，自身牌直伤每张递增1%；全队计数，同名叠加，重放不计数。</t>
+        </is>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>From team card 3 each round: own direct card damage +1% per card. Copies stack; replays do not count.</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>1条示例</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>第1/2张0%，第3/4/5张+1%/+2%/+3%。</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>Cards 1/2: 0%; cards 3/4/5: +1%/+2%/+3%.</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>2条示例</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>第3/4/5张+2%/+4%/+6%。</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>Cards 3/4/5: +2%/+4%/+6%.</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>品质</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>普通至无量，每条固定100基点；品质不增幅。</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Every tier grants exactly 1% per step per copy.</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>范围</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>物理/元素/多段/重箭直击；只看出牌者配装。</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>Own physical, elemental, multi-hit and Heavy Arrow card attacks.</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>固定伤害、自损、持续伤害、反应、装备触发不加。</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Excludes fixed damage, self-loss, DOT, reactions and gear procs.</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>重放</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>不增加计数，使用当前全队计数；下回合归零。</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>Replays use the current team count without advancing it; reset each round.</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>退休池</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>追风抽牌/回气/计数/减费；山河地势减费。</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>Retired random draw, AP, combo-count and cost-discount affixes.</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>旧档</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>定向转换退休项，优先省力→乘风，保留其余装备字段。</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="inlineStr">
+        <is>
+          <t>Convert only retired rolls; preserve the rest of each item.</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>待选洗炼</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>原/新结果同步转换，不重复扣费；始终可保留或采用。</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>Migrate both paid choices without spending sand again.</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>旧战斗</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>保存的战斗效果快照保留至结算，下场启用新配装。</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
+        <is>
+          <t>Saved battles retain their snapshots; new loadouts apply next battle.</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>存档范围</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>未加持久化字段；沿用原装备结构及存档校验。</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>No new serialized fields; existing gear schema is retained.</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>行为检查通过；视觉另行验收</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E7"/>
-  <printOptions horizontalCentered="1"/>
+  <autoFilter ref="A4:D16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
+++ b/docs/design/2026-09-04-project-design-tables/GameXXK_装备设计总表_2026-09-04.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_词缀目录" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_触发与接入审查" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04B_品质与数值基线" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04D_叠加上限与边际" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04E_一至六件边际" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04F_递减曲线" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04G_详细属性口径" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04H_追风递增与退休" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04C_名称显示入口" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_套装效果" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_套装术语" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_实现差异" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_百级最终属性" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_宝石总表" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_宝石品质边际" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_装备模板" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_至宝配装基准" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_掉落等级带" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_挂机金币现状" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07B_分解与工具经验" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07C_经济与工具边界" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07D_宝箱与行旅钱" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_来源校验" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02B_百分比宝石数值" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02C_宝石收益与表现" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07E_挂机与天赋预算" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07F_天赋分档价格" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="00_说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="04_词缀目录" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="04A_触发与接入审查" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04B_品质与数值基线" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04D_叠加上限与边际" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="04E_一至六件边际" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="04F_递减曲线" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="04G_详细属性口径" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="04H_追风递增与退休" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="04C_名称显示入口" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="05_套装效果" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="05A_套装术语" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="08_实现差异" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="01_百级最终属性" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="02_宝石总表" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="02A_宝石品质边际" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="03_装备模板" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="06_至宝配装基准" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="07_掉落等级带" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="07A_挂机金币现状" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="07B_分解与工具经验" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="07C_经济与工具边界" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="07D_宝箱与行旅钱" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="09_来源校验" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="02B_百分比宝石数值" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="02C_宝石收益与表现" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="07E_挂机与天赋预算" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="07F_天赋分档价格" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_说明'!$A$1:$B$15</definedName>
@@ -513,13 +513,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -542,7 +542,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="26000">
+            <a:ln w="26000">
               <a:solidFill>
                 <a:srgbClr val="244D57"/>
               </a:solidFill>
@@ -552,7 +552,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -577,7 +577,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="D99A33"/>
               </a:solidFill>
@@ -587,7 +587,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -615,8 +615,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -645,8 +645,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -673,13 +673,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -702,14 +702,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -734,14 +734,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -769,8 +769,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -796,8 +796,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -823,7 +823,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -838,9 +838,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -850,7 +850,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -865,9 +865,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -877,7 +877,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -892,14 +892,14 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:prstGeom prst="rect"/>
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
